--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -18427,6 +18427,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="786">
+      <c r="A786" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B786" t="n">
+        <v>0</v>
+      </c>
+      <c r="C786" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="D786" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="E786" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="F786" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="G786" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B787" t="n">
+        <v>350</v>
+      </c>
+      <c r="C787" t="n">
+        <v>9</v>
+      </c>
+      <c r="D787" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="E787" t="n">
+        <v>9</v>
+      </c>
+      <c r="F787" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="G787" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -18473,6 +18473,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="788">
+      <c r="A788" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B788" t="n">
+        <v>700</v>
+      </c>
+      <c r="C788" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="D788" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="E788" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="F788" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="G788" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -18496,6 +18496,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="789">
+      <c r="A789" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B789" t="n">
+        <v>0</v>
+      </c>
+      <c r="C789" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="D789" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="E789" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="F789" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="G789" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -18360,22 +18360,22 @@
     </row>
     <row r="783">
       <c r="A783" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B783" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C783" t="n">
-        <v>9.5</v>
+        <v>9.39999961853027</v>
       </c>
       <c r="D783" t="n">
-        <v>9.5</v>
+        <v>9.39999961853027</v>
       </c>
       <c r="E783" t="n">
-        <v>9.5</v>
+        <v>9.39999961853027</v>
       </c>
       <c r="F783" t="n">
-        <v>9.5</v>
+        <v>9.39999961853027</v>
       </c>
       <c r="G783" t="s">
         <v>7</v>
@@ -18383,10 +18383,10 @@
     </row>
     <row r="784">
       <c r="A784" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B784" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C784" t="n">
         <v>9.5</v>
@@ -18406,22 +18406,22 @@
     </row>
     <row r="785">
       <c r="A785" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B785" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="C785" t="n">
-        <v>9.44999980926514</v>
+        <v>9.5</v>
       </c>
       <c r="D785" t="n">
-        <v>9.44999980926514</v>
+        <v>9.5</v>
       </c>
       <c r="E785" t="n">
-        <v>9.44999980926514</v>
+        <v>9.5</v>
       </c>
       <c r="F785" t="n">
-        <v>9.44999980926514</v>
+        <v>9.5</v>
       </c>
       <c r="G785" t="s">
         <v>7</v>
@@ -18429,10 +18429,10 @@
     </row>
     <row r="786">
       <c r="A786" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B786" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="C786" t="n">
         <v>9.44999980926514</v>
@@ -18452,22 +18452,22 @@
     </row>
     <row r="787">
       <c r="A787" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B787" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C787" t="n">
-        <v>9</v>
+        <v>9.44999980926514</v>
       </c>
       <c r="D787" t="n">
-        <v>8.89999961853027</v>
+        <v>9.44999980926514</v>
       </c>
       <c r="E787" t="n">
-        <v>9</v>
+        <v>9.44999980926514</v>
       </c>
       <c r="F787" t="n">
-        <v>8.89999961853027</v>
+        <v>9.44999980926514</v>
       </c>
       <c r="G787" t="s">
         <v>7</v>
@@ -18475,22 +18475,22 @@
     </row>
     <row r="788">
       <c r="A788" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B788" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="C788" t="n">
-        <v>9.44999980926514</v>
+        <v>9</v>
       </c>
       <c r="D788" t="n">
-        <v>9.19999980926514</v>
+        <v>8.89999961853027</v>
       </c>
       <c r="E788" t="n">
-        <v>9.19999980926514</v>
+        <v>9</v>
       </c>
       <c r="F788" t="n">
-        <v>9.44999980926514</v>
+        <v>8.89999961853027</v>
       </c>
       <c r="G788" t="s">
         <v>7</v>
@@ -18498,24 +18498,47 @@
     </row>
     <row r="789">
       <c r="A789" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B789" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="C789" t="n">
         <v>9.44999980926514</v>
       </c>
       <c r="D789" t="n">
-        <v>9.44999980926514</v>
+        <v>9.19999980926514</v>
       </c>
       <c r="E789" t="n">
-        <v>9.44999980926514</v>
+        <v>9.19999980926514</v>
       </c>
       <c r="F789" t="n">
         <v>9.44999980926514</v>
       </c>
       <c r="G789" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B790" t="n">
+        <v>0</v>
+      </c>
+      <c r="C790" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="D790" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="E790" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="F790" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="G790" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -18542,6 +18542,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="791">
+      <c r="A791" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B791" t="n">
+        <v>0</v>
+      </c>
+      <c r="C791" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="D791" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="E791" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="F791" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="G791" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B792" t="n">
+        <v>0</v>
+      </c>
+      <c r="C792" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="D792" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="E792" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="F792" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="G792" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -447,7 +447,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>3.96673274040222</v>
+        <v>3.96673226356506</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G32" t="n">
-        <v>4.8286395072937</v>
+        <v>4.82863903045654</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G53" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>4.48583555221558</v>
+        <v>4.48583507537842</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>4.48583555221558</v>
+        <v>4.48583507537842</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G94" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G97" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>4.30953645706177</v>
+        <v>4.30953598022461</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G136" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G137" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G139" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G140" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G144" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G145" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G146" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G148" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G157" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G159" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G160" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>4.48583555221558</v>
+        <v>4.48583507537842</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G207" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G211" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G212" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G214" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>4.32912492752075</v>
+        <v>4.32912540435791</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G241" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G243" t="n">
-        <v>4.30953645706177</v>
+        <v>4.30953598022461</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G262" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95693802833557</v>
+        <v>3.95693778991699</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G276" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G277" t="n">
-        <v>3.60433959960938</v>
+        <v>3.6043393611908</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G281" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G290" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G294" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G296" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G299" t="n">
-        <v>3.70228362083435</v>
+        <v>3.70228338241577</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G306" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>4.15282535552979</v>
+        <v>4.15282583236694</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G322" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G323" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G330" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G332" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G346" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G356" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G358" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G359" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G380" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G382" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G383" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G386" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G388" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G403" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G408" t="n">
-        <v>3.70228362083435</v>
+        <v>3.70228338241577</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G409" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G410" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G423" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G424" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G425" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G426" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G427" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G428" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G432" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G433" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G435" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G439" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G440" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G443" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G444" t="n">
-        <v>4.32912492752075</v>
+        <v>4.32912540435791</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -21001,7 +21001,7 @@
         <v>525</v>
       </c>
       <c r="C794" t="n">
-        <v>9.35000038146973</v>
+        <v>9.75</v>
       </c>
       <c r="D794" t="n">
         <v>9.14999961853027</v>
@@ -21016,6 +21016,32 @@
         <v>9.75</v>
       </c>
       <c r="H794" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B795" t="n">
+        <v>350</v>
+      </c>
+      <c r="C795" t="n">
+        <v>9.55000019073486</v>
+      </c>
+      <c r="D795" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="E795" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="F795" t="n">
+        <v>9.55000019073486</v>
+      </c>
+      <c r="G795" t="n">
+        <v>9.55000019073486</v>
+      </c>
+      <c r="H795" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -21045,6 +21045,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="796">
+      <c r="A796" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B796" t="n">
+        <v>350</v>
+      </c>
+      <c r="C796" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D796" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E796" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="F796" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="G796" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="H796" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -21071,6 +21071,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="797">
+      <c r="A797" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B797" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C797" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="D797" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="E797" t="n">
+        <v>9</v>
+      </c>
+      <c r="F797" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="G797" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="H797" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -18703,6 +18703,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="798">
+      <c r="A798" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B798" t="n">
+        <v>0</v>
+      </c>
+      <c r="C798" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="D798" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="E798" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="F798" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="G798" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -18818,6 +18818,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="803">
+      <c r="A803" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B803" t="n">
+        <v>0</v>
+      </c>
+      <c r="C803" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="D803" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="E803" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="F803" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="G803" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -18841,6 +18841,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="804">
+      <c r="A804" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B804" t="n">
+        <v>0</v>
+      </c>
+      <c r="C804" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="D804" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="E804" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="F804" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="G804" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -18864,6 +18864,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="805">
+      <c r="A805" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B805" t="n">
+        <v>0</v>
+      </c>
+      <c r="C805" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="D805" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="E805" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="F805" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="G805" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -18887,6 +18887,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B806" t="n">
+        <v>0</v>
+      </c>
+      <c r="C806" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="D806" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="E806" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="F806" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="G806" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -18933,6 +18933,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B808" t="n">
+        <v>0</v>
+      </c>
+      <c r="C808" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="D808" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="E808" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="F808" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="G808" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -447,7 +447,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>3.96673274040222</v>
+        <v>3.96673226356506</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G32" t="n">
-        <v>4.8286395072937</v>
+        <v>4.82863903045654</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G53" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>4.48583555221558</v>
+        <v>4.48583507537842</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>4.48583555221558</v>
+        <v>4.48583507537842</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G94" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G97" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>4.30953645706177</v>
+        <v>4.30953598022461</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G136" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G137" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G139" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G140" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G144" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G145" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G146" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G148" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G157" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G159" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G160" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>4.48583555221558</v>
+        <v>4.48583507537842</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G207" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G211" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G212" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G214" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>4.32912492752075</v>
+        <v>4.32912540435791</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G241" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G243" t="n">
-        <v>4.30953645706177</v>
+        <v>4.30953598022461</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G262" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95693802833557</v>
+        <v>3.95693778991699</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G276" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G277" t="n">
-        <v>3.60433959960938</v>
+        <v>3.6043393611908</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G281" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G290" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G294" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G296" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G299" t="n">
-        <v>3.70228362083435</v>
+        <v>3.70228338241577</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G306" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>4.15282535552979</v>
+        <v>4.15282583236694</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G322" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G323" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G330" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G332" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G346" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G356" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G358" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G359" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G380" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G382" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G383" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G386" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G388" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G403" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G408" t="n">
-        <v>3.70228362083435</v>
+        <v>3.70228338241577</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G409" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G410" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G423" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G424" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G425" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G426" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G427" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G428" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G432" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G433" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G435" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G439" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G440" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G443" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G444" t="n">
-        <v>4.32912492752075</v>
+        <v>4.32912540435791</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -21432,6 +21432,32 @@
         <v>9</v>
       </c>
       <c r="H810" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B811" t="n">
+        <v>1575</v>
+      </c>
+      <c r="C811" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="D811" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="E811" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F811" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="G811" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="H811" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -21461,6 +21461,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="812">
+      <c r="A812" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B812" t="n">
+        <v>700</v>
+      </c>
+      <c r="C812" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="D812" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="E812" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F812" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="G812" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="H812" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>3.96673226356506</v>
+        <v>3.96673274040222</v>
       </c>
       <c r="H3" t="n">
         <v>7700</v>
@@ -601,7 +601,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H8" t="n">
         <v>4200</v>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.89720058441162</v>
+        <v>4.89720010757446</v>
       </c>
       <c r="H28" t="n">
         <v>6300</v>
@@ -1210,7 +1210,7 @@
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89720058441162</v>
+        <v>4.89720010757446</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G32" t="n">
-        <v>4.82863903045654</v>
+        <v>4.8286395072937</v>
       </c>
       <c r="H32" t="n">
         <v>350</v>
@@ -1326,7 +1326,7 @@
         <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>4.89720058441162</v>
+        <v>4.89720010757446</v>
       </c>
       <c r="H33" t="n">
         <v>3500</v>
@@ -1500,7 +1500,7 @@
         <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>4.89720058441162</v>
+        <v>4.89720010757446</v>
       </c>
       <c r="H39" t="n">
         <v>22400</v>
@@ -1558,7 +1558,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>4.89720058441162</v>
+        <v>4.89720010757446</v>
       </c>
       <c r="H41" t="n">
         <v>1400</v>
@@ -1906,7 +1906,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G53" t="n">
-        <v>4.34871435165405</v>
+        <v>4.34871387481689</v>
       </c>
       <c r="H53" t="n">
         <v>1750</v>
@@ -2776,7 +2776,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>4.48583507537842</v>
+        <v>4.48583555221558</v>
       </c>
       <c r="H83" t="n">
         <v>4900</v>
@@ -2805,7 +2805,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>4.48583507537842</v>
+        <v>4.48583555221558</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G94" t="n">
-        <v>4.34871435165405</v>
+        <v>4.34871387481689</v>
       </c>
       <c r="H94" t="n">
         <v>3150</v>
@@ -3124,7 +3124,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>4.34871435165405</v>
+        <v>4.34871387481689</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>4.34871435165405</v>
+        <v>4.34871387481689</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G97" t="n">
-        <v>4.34871435165405</v>
+        <v>4.34871387481689</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>4.30953598022461</v>
+        <v>4.30953645706177</v>
       </c>
       <c r="H99" t="n">
         <v>700</v>
@@ -4313,7 +4313,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G136" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H136" t="n">
         <v>700</v>
@@ -4342,7 +4342,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G137" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G139" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G140" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G144" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G145" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G146" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G148" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G157" t="n">
-        <v>4.72090148925781</v>
+        <v>4.72090101242065</v>
       </c>
       <c r="H157" t="n">
         <v>1050</v>
@@ -4951,7 +4951,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.72090148925781</v>
+        <v>4.72090101242065</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G159" t="n">
-        <v>4.72090148925781</v>
+        <v>4.72090101242065</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G160" t="n">
-        <v>4.72090148925781</v>
+        <v>4.72090101242065</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>4.48583507537842</v>
+        <v>4.48583555221558</v>
       </c>
       <c r="H172" t="n">
         <v>700</v>
@@ -6169,7 +6169,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H200" t="n">
         <v>700</v>
@@ -6198,7 +6198,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G207" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H207" t="n">
         <v>350</v>
@@ -6401,7 +6401,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G211" t="n">
-        <v>4.0352931022644</v>
+        <v>4.03529262542725</v>
       </c>
       <c r="H211" t="n">
         <v>2100</v>
@@ -6517,7 +6517,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G212" t="n">
-        <v>4.0352931022644</v>
+        <v>4.03529262542725</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>4.0352931022644</v>
+        <v>4.03529262542725</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G214" t="n">
-        <v>4.0352931022644</v>
+        <v>4.03529262542725</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>4.32912540435791</v>
+        <v>4.32912492752075</v>
       </c>
       <c r="H216" t="n">
         <v>1400</v>
@@ -7358,7 +7358,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G241" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H241" t="n">
         <v>1400</v>
@@ -7387,7 +7387,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G243" t="n">
-        <v>4.30953598022461</v>
+        <v>4.30953645706177</v>
       </c>
       <c r="H243" t="n">
         <v>7350</v>
@@ -7967,7 +7967,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G262" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H262" t="n">
         <v>3500</v>
@@ -8228,7 +8228,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95693778991699</v>
+        <v>3.95693802833557</v>
       </c>
       <c r="H271" t="n">
         <v>700</v>
@@ -8373,7 +8373,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G276" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H276" t="n">
         <v>14000</v>
@@ -8402,7 +8402,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G277" t="n">
-        <v>3.6043393611908</v>
+        <v>3.60433959960938</v>
       </c>
       <c r="H277" t="n">
         <v>7000</v>
@@ -8489,7 +8489,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>3.72187209129333</v>
+        <v>3.72187232971191</v>
       </c>
       <c r="H280" t="n">
         <v>1050</v>
@@ -8518,7 +8518,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G281" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H281" t="n">
         <v>1750</v>
@@ -8547,7 +8547,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H282" t="n">
         <v>1050</v>
@@ -8779,7 +8779,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G290" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H290" t="n">
         <v>4900</v>
@@ -8808,7 +8808,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H291" t="n">
         <v>1050</v>
@@ -8837,7 +8837,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H292" t="n">
         <v>1750</v>
@@ -8866,7 +8866,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H293" t="n">
         <v>700</v>
@@ -8895,7 +8895,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G294" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H294" t="n">
         <v>700</v>
@@ -8953,7 +8953,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G296" t="n">
-        <v>3.7806384563446</v>
+        <v>3.78063869476318</v>
       </c>
       <c r="H296" t="n">
         <v>1400</v>
@@ -9040,7 +9040,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G299" t="n">
-        <v>3.70228338241577</v>
+        <v>3.70228362083435</v>
       </c>
       <c r="H299" t="n">
         <v>1400</v>
@@ -9156,7 +9156,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H303" t="n">
         <v>700</v>
@@ -9214,7 +9214,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H305" t="n">
         <v>2450</v>
@@ -9243,7 +9243,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G306" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H306" t="n">
         <v>5600</v>
@@ -9417,7 +9417,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>4.15282583236694</v>
+        <v>4.15282535552979</v>
       </c>
       <c r="H312" t="n">
         <v>4550</v>
@@ -9707,7 +9707,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G322" t="n">
-        <v>4.17241525650024</v>
+        <v>4.17241477966309</v>
       </c>
       <c r="H322" t="n">
         <v>1050</v>
@@ -9736,7 +9736,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G323" t="n">
-        <v>4.17241525650024</v>
+        <v>4.17241477966309</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G330" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H330" t="n">
         <v>2100</v>
@@ -9968,7 +9968,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.7806384563446</v>
+        <v>3.78063869476318</v>
       </c>
       <c r="H331" t="n">
         <v>4550</v>
@@ -9997,7 +9997,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G332" t="n">
-        <v>3.7806384563446</v>
+        <v>3.78063869476318</v>
       </c>
       <c r="H332" t="n">
         <v>2100</v>
@@ -10316,7 +10316,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H343" t="n">
         <v>3500</v>
@@ -10345,7 +10345,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G346" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H349" t="n">
         <v>350</v>
@@ -10519,7 +10519,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H351" t="n">
         <v>350</v>
@@ -10693,7 +10693,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G356" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H356" t="n">
         <v>4200</v>
@@ -10751,7 +10751,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G358" t="n">
-        <v>3.7806384563446</v>
+        <v>3.78063869476318</v>
       </c>
       <c r="H358" t="n">
         <v>7350</v>
@@ -10780,7 +10780,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G359" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H359" t="n">
         <v>8050</v>
@@ -11041,7 +11041,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H368" t="n">
         <v>1400</v>
@@ -11331,7 +11331,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>4.0352931022644</v>
+        <v>4.03529262542725</v>
       </c>
       <c r="H378" t="n">
         <v>1050</v>
@@ -11389,7 +11389,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G380" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H380" t="n">
         <v>2100</v>
@@ -11418,7 +11418,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G382" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G383" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H383" t="n">
         <v>350</v>
@@ -11505,7 +11505,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.7806384563446</v>
+        <v>3.78063869476318</v>
       </c>
       <c r="H385" t="n">
         <v>700</v>
@@ -11563,7 +11563,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G386" t="n">
-        <v>3.72187209129333</v>
+        <v>3.72187232971191</v>
       </c>
       <c r="H386" t="n">
         <v>11550</v>
@@ -11592,7 +11592,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.72187209129333</v>
+        <v>3.72187232971191</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G388" t="n">
-        <v>3.72187209129333</v>
+        <v>3.72187232971191</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H400" t="n">
         <v>2450</v>
@@ -11998,7 +11998,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H401" t="n">
         <v>350</v>
@@ -12027,7 +12027,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G403" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G408" t="n">
-        <v>3.70228338241577</v>
+        <v>3.70228362083435</v>
       </c>
       <c r="H408" t="n">
         <v>700</v>
@@ -12230,7 +12230,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G409" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H409" t="n">
         <v>1750</v>
@@ -12259,7 +12259,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G410" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12636,7 +12636,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G423" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H423" t="n">
         <v>350</v>
@@ -12665,7 +12665,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G424" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G425" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G426" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G427" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -12781,7 +12781,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G428" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G432" t="n">
-        <v>3.72187209129333</v>
+        <v>3.72187232971191</v>
       </c>
       <c r="H432" t="n">
         <v>2100</v>
@@ -12926,7 +12926,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G433" t="n">
-        <v>3.72187209129333</v>
+        <v>3.72187232971191</v>
       </c>
       <c r="H433" t="n">
         <v>7350</v>
@@ -12984,7 +12984,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G435" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H435" t="n">
         <v>6300</v>
@@ -13100,7 +13100,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G439" t="n">
-        <v>4.17241525650024</v>
+        <v>4.17241477966309</v>
       </c>
       <c r="H439" t="n">
         <v>700</v>
@@ -13129,7 +13129,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G440" t="n">
-        <v>4.17241525650024</v>
+        <v>4.17241477966309</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H442" t="n">
         <v>5950</v>
@@ -13216,7 +13216,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G443" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G444" t="n">
-        <v>4.32912540435791</v>
+        <v>4.32912492752075</v>
       </c>
       <c r="H444" t="n">
         <v>5600</v>
@@ -23923,6 +23923,35 @@
         <v>700</v>
       </c>
       <c r="I812" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="s">
+        <v>9</v>
+      </c>
+      <c r="B813" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C813" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="D813" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="E813" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="F813" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="G813" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="H813" t="n">
+        <v>175</v>
+      </c>
+      <c r="I813" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -23955,6 +23955,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="814">
+      <c r="A814" t="s">
+        <v>9</v>
+      </c>
+      <c r="B814" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C814" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="D814" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="E814" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="F814" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="G814" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="H814" t="n">
+        <v>0</v>
+      </c>
+      <c r="I814" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>3.96673274040222</v>
+        <v>3.96673226356506</v>
       </c>
       <c r="H3" t="n">
         <v>7700</v>
@@ -601,7 +601,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H8" t="n">
         <v>4200</v>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H28" t="n">
         <v>6300</v>
@@ -1210,7 +1210,7 @@
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G32" t="n">
-        <v>4.8286395072937</v>
+        <v>4.82863903045654</v>
       </c>
       <c r="H32" t="n">
         <v>350</v>
@@ -1326,7 +1326,7 @@
         <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H33" t="n">
         <v>3500</v>
@@ -1500,7 +1500,7 @@
         <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H39" t="n">
         <v>22400</v>
@@ -1558,7 +1558,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H41" t="n">
         <v>1400</v>
@@ -1906,7 +1906,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G53" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H53" t="n">
         <v>1750</v>
@@ -2776,7 +2776,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>4.48583555221558</v>
+        <v>4.48583507537842</v>
       </c>
       <c r="H83" t="n">
         <v>4900</v>
@@ -2805,7 +2805,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>4.48583555221558</v>
+        <v>4.48583507537842</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G94" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H94" t="n">
         <v>3150</v>
@@ -3124,7 +3124,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G97" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>4.30953645706177</v>
+        <v>4.30953598022461</v>
       </c>
       <c r="H99" t="n">
         <v>700</v>
@@ -4313,7 +4313,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G136" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H136" t="n">
         <v>700</v>
@@ -4342,7 +4342,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G137" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G139" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G140" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G144" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G145" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G146" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G148" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G157" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H157" t="n">
         <v>1050</v>
@@ -4951,7 +4951,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G159" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G160" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>4.48583555221558</v>
+        <v>4.48583507537842</v>
       </c>
       <c r="H172" t="n">
         <v>700</v>
@@ -6169,7 +6169,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H200" t="n">
         <v>700</v>
@@ -6198,7 +6198,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G207" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H207" t="n">
         <v>350</v>
@@ -6401,7 +6401,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G211" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H211" t="n">
         <v>2100</v>
@@ -6517,7 +6517,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G212" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G214" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>4.32912492752075</v>
+        <v>4.32912540435791</v>
       </c>
       <c r="H216" t="n">
         <v>1400</v>
@@ -7358,7 +7358,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G241" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H241" t="n">
         <v>1400</v>
@@ -7387,7 +7387,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G243" t="n">
-        <v>4.30953645706177</v>
+        <v>4.30953598022461</v>
       </c>
       <c r="H243" t="n">
         <v>7350</v>
@@ -7967,7 +7967,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G262" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H262" t="n">
         <v>3500</v>
@@ -8228,7 +8228,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95693802833557</v>
+        <v>3.95693778991699</v>
       </c>
       <c r="H271" t="n">
         <v>700</v>
@@ -8373,7 +8373,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G276" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H276" t="n">
         <v>14000</v>
@@ -8402,7 +8402,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G277" t="n">
-        <v>3.60433959960938</v>
+        <v>3.6043393611908</v>
       </c>
       <c r="H277" t="n">
         <v>7000</v>
@@ -8489,7 +8489,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H280" t="n">
         <v>1050</v>
@@ -8518,7 +8518,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G281" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H281" t="n">
         <v>1750</v>
@@ -8547,7 +8547,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H282" t="n">
         <v>1050</v>
@@ -8779,7 +8779,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G290" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H290" t="n">
         <v>4900</v>
@@ -8808,7 +8808,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H291" t="n">
         <v>1050</v>
@@ -8837,7 +8837,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H292" t="n">
         <v>1750</v>
@@ -8866,7 +8866,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H293" t="n">
         <v>700</v>
@@ -8895,7 +8895,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G294" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H294" t="n">
         <v>700</v>
@@ -8953,7 +8953,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G296" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H296" t="n">
         <v>1400</v>
@@ -9040,7 +9040,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G299" t="n">
-        <v>3.70228362083435</v>
+        <v>3.70228338241577</v>
       </c>
       <c r="H299" t="n">
         <v>1400</v>
@@ -9156,7 +9156,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H303" t="n">
         <v>700</v>
@@ -9214,7 +9214,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H305" t="n">
         <v>2450</v>
@@ -9243,7 +9243,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G306" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H306" t="n">
         <v>5600</v>
@@ -9417,7 +9417,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>4.15282535552979</v>
+        <v>4.15282583236694</v>
       </c>
       <c r="H312" t="n">
         <v>4550</v>
@@ -9707,7 +9707,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G322" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H322" t="n">
         <v>1050</v>
@@ -9736,7 +9736,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G323" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G330" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H330" t="n">
         <v>2100</v>
@@ -9968,7 +9968,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H331" t="n">
         <v>4550</v>
@@ -9997,7 +9997,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G332" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H332" t="n">
         <v>2100</v>
@@ -10316,7 +10316,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H343" t="n">
         <v>3500</v>
@@ -10345,7 +10345,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G346" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H349" t="n">
         <v>350</v>
@@ -10519,7 +10519,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H351" t="n">
         <v>350</v>
@@ -10693,7 +10693,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G356" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H356" t="n">
         <v>4200</v>
@@ -10751,7 +10751,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G358" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H358" t="n">
         <v>7350</v>
@@ -10780,7 +10780,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G359" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H359" t="n">
         <v>8050</v>
@@ -11041,7 +11041,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H368" t="n">
         <v>1400</v>
@@ -11331,7 +11331,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H378" t="n">
         <v>1050</v>
@@ -11389,7 +11389,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G380" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H380" t="n">
         <v>2100</v>
@@ -11418,7 +11418,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G382" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G383" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H383" t="n">
         <v>350</v>
@@ -11505,7 +11505,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H385" t="n">
         <v>700</v>
@@ -11563,7 +11563,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G386" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H386" t="n">
         <v>11550</v>
@@ -11592,7 +11592,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G388" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H400" t="n">
         <v>2450</v>
@@ -11998,7 +11998,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H401" t="n">
         <v>350</v>
@@ -12027,7 +12027,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G403" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G408" t="n">
-        <v>3.70228362083435</v>
+        <v>3.70228338241577</v>
       </c>
       <c r="H408" t="n">
         <v>700</v>
@@ -12230,7 +12230,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G409" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H409" t="n">
         <v>1750</v>
@@ -12259,7 +12259,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G410" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12636,7 +12636,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G423" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H423" t="n">
         <v>350</v>
@@ -12665,7 +12665,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G424" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G425" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G426" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G427" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -12781,7 +12781,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G428" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G432" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H432" t="n">
         <v>2100</v>
@@ -12926,7 +12926,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G433" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H433" t="n">
         <v>7350</v>
@@ -12984,7 +12984,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G435" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H435" t="n">
         <v>6300</v>
@@ -13100,7 +13100,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G439" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H439" t="n">
         <v>700</v>
@@ -13129,7 +13129,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G440" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H442" t="n">
         <v>5950</v>
@@ -13216,7 +13216,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G443" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G444" t="n">
-        <v>4.32912492752075</v>
+        <v>4.32912540435791</v>
       </c>
       <c r="H444" t="n">
         <v>5600</v>
@@ -23981,6 +23981,35 @@
         <v>0</v>
       </c>
       <c r="I814" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="s">
+        <v>9</v>
+      </c>
+      <c r="B815" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C815" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="D815" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="E815" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="F815" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="G815" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="H815" t="n">
+        <v>0</v>
+      </c>
+      <c r="I815" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>3.96673226356506</v>
+        <v>3.96673274040222</v>
       </c>
       <c r="H3" t="n">
         <v>7700</v>
@@ -601,7 +601,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H8" t="n">
         <v>4200</v>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.89720058441162</v>
+        <v>4.89720010757446</v>
       </c>
       <c r="H28" t="n">
         <v>6300</v>
@@ -1210,7 +1210,7 @@
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89720058441162</v>
+        <v>4.89720010757446</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G32" t="n">
-        <v>4.82863903045654</v>
+        <v>4.8286395072937</v>
       </c>
       <c r="H32" t="n">
         <v>350</v>
@@ -1326,7 +1326,7 @@
         <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>4.89720058441162</v>
+        <v>4.89720010757446</v>
       </c>
       <c r="H33" t="n">
         <v>3500</v>
@@ -1500,7 +1500,7 @@
         <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>4.89720058441162</v>
+        <v>4.89720010757446</v>
       </c>
       <c r="H39" t="n">
         <v>22400</v>
@@ -1558,7 +1558,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>4.89720058441162</v>
+        <v>4.89720010757446</v>
       </c>
       <c r="H41" t="n">
         <v>1400</v>
@@ -1906,7 +1906,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G53" t="n">
-        <v>4.34871435165405</v>
+        <v>4.34871387481689</v>
       </c>
       <c r="H53" t="n">
         <v>1750</v>
@@ -2776,7 +2776,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>4.48583507537842</v>
+        <v>4.48583555221558</v>
       </c>
       <c r="H83" t="n">
         <v>4900</v>
@@ -2805,7 +2805,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>4.48583507537842</v>
+        <v>4.48583555221558</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G94" t="n">
-        <v>4.34871435165405</v>
+        <v>4.34871387481689</v>
       </c>
       <c r="H94" t="n">
         <v>3150</v>
@@ -3124,7 +3124,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>4.34871435165405</v>
+        <v>4.34871387481689</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>4.34871435165405</v>
+        <v>4.34871387481689</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G97" t="n">
-        <v>4.34871435165405</v>
+        <v>4.34871387481689</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>4.30953598022461</v>
+        <v>4.30953645706177</v>
       </c>
       <c r="H99" t="n">
         <v>700</v>
@@ -4313,7 +4313,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G136" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H136" t="n">
         <v>700</v>
@@ -4342,7 +4342,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G137" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G139" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G140" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G144" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G145" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G146" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G148" t="n">
-        <v>4.77966785430908</v>
+        <v>4.77966737747192</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G157" t="n">
-        <v>4.72090148925781</v>
+        <v>4.72090101242065</v>
       </c>
       <c r="H157" t="n">
         <v>1050</v>
@@ -4951,7 +4951,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.72090148925781</v>
+        <v>4.72090101242065</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G159" t="n">
-        <v>4.72090148925781</v>
+        <v>4.72090101242065</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G160" t="n">
-        <v>4.72090148925781</v>
+        <v>4.72090101242065</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>4.48583507537842</v>
+        <v>4.48583555221558</v>
       </c>
       <c r="H172" t="n">
         <v>700</v>
@@ -6169,7 +6169,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H200" t="n">
         <v>700</v>
@@ -6198,7 +6198,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G207" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H207" t="n">
         <v>350</v>
@@ -6401,7 +6401,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G211" t="n">
-        <v>4.0352931022644</v>
+        <v>4.03529262542725</v>
       </c>
       <c r="H211" t="n">
         <v>2100</v>
@@ -6517,7 +6517,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G212" t="n">
-        <v>4.0352931022644</v>
+        <v>4.03529262542725</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>4.0352931022644</v>
+        <v>4.03529262542725</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G214" t="n">
-        <v>4.0352931022644</v>
+        <v>4.03529262542725</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>4.32912540435791</v>
+        <v>4.32912492752075</v>
       </c>
       <c r="H216" t="n">
         <v>1400</v>
@@ -7358,7 +7358,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G241" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H241" t="n">
         <v>1400</v>
@@ -7387,7 +7387,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G243" t="n">
-        <v>4.30953598022461</v>
+        <v>4.30953645706177</v>
       </c>
       <c r="H243" t="n">
         <v>7350</v>
@@ -7967,7 +7967,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G262" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H262" t="n">
         <v>3500</v>
@@ -8228,7 +8228,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95693778991699</v>
+        <v>3.95693802833557</v>
       </c>
       <c r="H271" t="n">
         <v>700</v>
@@ -8373,7 +8373,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G276" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H276" t="n">
         <v>14000</v>
@@ -8402,7 +8402,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G277" t="n">
-        <v>3.6043393611908</v>
+        <v>3.60433959960938</v>
       </c>
       <c r="H277" t="n">
         <v>7000</v>
@@ -8489,7 +8489,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>3.72187209129333</v>
+        <v>3.72187232971191</v>
       </c>
       <c r="H280" t="n">
         <v>1050</v>
@@ -8518,7 +8518,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G281" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H281" t="n">
         <v>1750</v>
@@ -8547,7 +8547,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H282" t="n">
         <v>1050</v>
@@ -8779,7 +8779,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G290" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H290" t="n">
         <v>4900</v>
@@ -8808,7 +8808,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H291" t="n">
         <v>1050</v>
@@ -8837,7 +8837,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H292" t="n">
         <v>1750</v>
@@ -8866,7 +8866,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H293" t="n">
         <v>700</v>
@@ -8895,7 +8895,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G294" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H294" t="n">
         <v>700</v>
@@ -8953,7 +8953,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G296" t="n">
-        <v>3.7806384563446</v>
+        <v>3.78063869476318</v>
       </c>
       <c r="H296" t="n">
         <v>1400</v>
@@ -9040,7 +9040,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G299" t="n">
-        <v>3.70228338241577</v>
+        <v>3.70228362083435</v>
       </c>
       <c r="H299" t="n">
         <v>1400</v>
@@ -9156,7 +9156,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H303" t="n">
         <v>700</v>
@@ -9214,7 +9214,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H305" t="n">
         <v>2450</v>
@@ -9243,7 +9243,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G306" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H306" t="n">
         <v>5600</v>
@@ -9417,7 +9417,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>4.15282583236694</v>
+        <v>4.15282535552979</v>
       </c>
       <c r="H312" t="n">
         <v>4550</v>
@@ -9707,7 +9707,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G322" t="n">
-        <v>4.17241525650024</v>
+        <v>4.17241477966309</v>
       </c>
       <c r="H322" t="n">
         <v>1050</v>
@@ -9736,7 +9736,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G323" t="n">
-        <v>4.17241525650024</v>
+        <v>4.17241477966309</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G330" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H330" t="n">
         <v>2100</v>
@@ -9968,7 +9968,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.7806384563446</v>
+        <v>3.78063869476318</v>
       </c>
       <c r="H331" t="n">
         <v>4550</v>
@@ -9997,7 +9997,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G332" t="n">
-        <v>3.7806384563446</v>
+        <v>3.78063869476318</v>
       </c>
       <c r="H332" t="n">
         <v>2100</v>
@@ -10316,7 +10316,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H343" t="n">
         <v>3500</v>
@@ -10345,7 +10345,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G346" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H349" t="n">
         <v>350</v>
@@ -10519,7 +10519,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H351" t="n">
         <v>350</v>
@@ -10693,7 +10693,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G356" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H356" t="n">
         <v>4200</v>
@@ -10751,7 +10751,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G358" t="n">
-        <v>3.7806384563446</v>
+        <v>3.78063869476318</v>
       </c>
       <c r="H358" t="n">
         <v>7350</v>
@@ -10780,7 +10780,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G359" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H359" t="n">
         <v>8050</v>
@@ -11041,7 +11041,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>3.89817142486572</v>
+        <v>3.8981716632843</v>
       </c>
       <c r="H368" t="n">
         <v>1400</v>
@@ -11331,7 +11331,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>4.0352931022644</v>
+        <v>4.03529262542725</v>
       </c>
       <c r="H378" t="n">
         <v>1050</v>
@@ -11389,7 +11389,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G380" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H380" t="n">
         <v>2100</v>
@@ -11418,7 +11418,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G382" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G383" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H383" t="n">
         <v>350</v>
@@ -11505,7 +11505,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.7806384563446</v>
+        <v>3.78063869476318</v>
       </c>
       <c r="H385" t="n">
         <v>700</v>
@@ -11563,7 +11563,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G386" t="n">
-        <v>3.72187209129333</v>
+        <v>3.72187232971191</v>
       </c>
       <c r="H386" t="n">
         <v>11550</v>
@@ -11592,7 +11592,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.72187209129333</v>
+        <v>3.72187232971191</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G388" t="n">
-        <v>3.72187209129333</v>
+        <v>3.72187232971191</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>3.80022740364075</v>
+        <v>3.80022764205933</v>
       </c>
       <c r="H400" t="n">
         <v>2450</v>
@@ -11998,7 +11998,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H401" t="n">
         <v>350</v>
@@ -12027,7 +12027,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G403" t="n">
-        <v>3.81981658935547</v>
+        <v>3.81981635093689</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G408" t="n">
-        <v>3.70228338241577</v>
+        <v>3.70228362083435</v>
       </c>
       <c r="H408" t="n">
         <v>700</v>
@@ -12230,7 +12230,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G409" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H409" t="n">
         <v>1750</v>
@@ -12259,7 +12259,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G410" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12636,7 +12636,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G423" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H423" t="n">
         <v>350</v>
@@ -12665,7 +12665,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G424" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G425" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G426" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G427" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -12781,7 +12781,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G428" t="n">
-        <v>3.58475065231323</v>
+        <v>3.58475089073181</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G432" t="n">
-        <v>3.72187209129333</v>
+        <v>3.72187232971191</v>
       </c>
       <c r="H432" t="n">
         <v>2100</v>
@@ -12926,7 +12926,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G433" t="n">
-        <v>3.72187209129333</v>
+        <v>3.72187232971191</v>
       </c>
       <c r="H433" t="n">
         <v>7350</v>
@@ -12984,7 +12984,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G435" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H435" t="n">
         <v>6300</v>
@@ -13100,7 +13100,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G439" t="n">
-        <v>4.17241525650024</v>
+        <v>4.17241477966309</v>
       </c>
       <c r="H439" t="n">
         <v>700</v>
@@ -13129,7 +13129,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G440" t="n">
-        <v>4.17241525650024</v>
+        <v>4.17241477966309</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H442" t="n">
         <v>5950</v>
@@ -13216,7 +13216,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G443" t="n">
-        <v>4.21159267425537</v>
+        <v>4.21159219741821</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G444" t="n">
-        <v>4.32912540435791</v>
+        <v>4.32912492752075</v>
       </c>
       <c r="H444" t="n">
         <v>5600</v>
@@ -24010,6 +24010,35 @@
         <v>0</v>
       </c>
       <c r="I815" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="s">
+        <v>9</v>
+      </c>
+      <c r="B816" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C816" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="D816" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="E816" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="F816" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="G816" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="H816" t="n">
+        <v>0</v>
+      </c>
+      <c r="I816" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -24042,6 +24042,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="817">
+      <c r="A817" t="s">
+        <v>9</v>
+      </c>
+      <c r="B817" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C817" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="D817" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="E817" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="F817" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="G817" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="H817" t="n">
+        <v>0</v>
+      </c>
+      <c r="I817" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="s">
+        <v>9</v>
+      </c>
+      <c r="B818" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C818" t="n">
+        <v>8.69999980926514</v>
+      </c>
+      <c r="D818" t="n">
+        <v>8.69999980926514</v>
+      </c>
+      <c r="E818" t="n">
+        <v>8.35000038146973</v>
+      </c>
+      <c r="F818" t="n">
+        <v>8.35000038146973</v>
+      </c>
+      <c r="G818" t="n">
+        <v>8.35000038146973</v>
+      </c>
+      <c r="H818" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I818" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -24100,6 +24100,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="819">
+      <c r="A819" t="s">
+        <v>9</v>
+      </c>
+      <c r="B819" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C819" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="D819" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="E819" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="F819" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="G819" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="H819" t="n">
+        <v>350</v>
+      </c>
+      <c r="I819" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>3.96673274040222</v>
+        <v>3.96673226356506</v>
       </c>
       <c r="H3" t="n">
         <v>7700</v>
@@ -601,7 +601,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H8" t="n">
         <v>4200</v>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H28" t="n">
         <v>6300</v>
@@ -1210,7 +1210,7 @@
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G32" t="n">
-        <v>4.8286395072937</v>
+        <v>4.82863903045654</v>
       </c>
       <c r="H32" t="n">
         <v>350</v>
@@ -1326,7 +1326,7 @@
         <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H33" t="n">
         <v>3500</v>
@@ -1500,7 +1500,7 @@
         <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H39" t="n">
         <v>22400</v>
@@ -1558,7 +1558,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>4.89720010757446</v>
+        <v>4.89720058441162</v>
       </c>
       <c r="H41" t="n">
         <v>1400</v>
@@ -1906,7 +1906,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G53" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H53" t="n">
         <v>1750</v>
@@ -2776,7 +2776,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>4.48583555221558</v>
+        <v>4.48583507537842</v>
       </c>
       <c r="H83" t="n">
         <v>4900</v>
@@ -2805,7 +2805,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>4.48583555221558</v>
+        <v>4.48583507537842</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G94" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H94" t="n">
         <v>3150</v>
@@ -3124,7 +3124,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G97" t="n">
-        <v>4.34871387481689</v>
+        <v>4.34871435165405</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>4.30953645706177</v>
+        <v>4.30953598022461</v>
       </c>
       <c r="H99" t="n">
         <v>700</v>
@@ -4313,7 +4313,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G136" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H136" t="n">
         <v>700</v>
@@ -4342,7 +4342,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G137" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G139" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G140" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G144" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G145" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G146" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G148" t="n">
-        <v>4.77966737747192</v>
+        <v>4.77966785430908</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G157" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H157" t="n">
         <v>1050</v>
@@ -4951,7 +4951,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G159" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G160" t="n">
-        <v>4.72090101242065</v>
+        <v>4.72090148925781</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>4.48583555221558</v>
+        <v>4.48583507537842</v>
       </c>
       <c r="H172" t="n">
         <v>700</v>
@@ -6169,7 +6169,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H200" t="n">
         <v>700</v>
@@ -6198,7 +6198,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G207" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H207" t="n">
         <v>350</v>
@@ -6401,7 +6401,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G211" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H211" t="n">
         <v>2100</v>
@@ -6517,7 +6517,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G212" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G214" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>4.32912492752075</v>
+        <v>4.32912540435791</v>
       </c>
       <c r="H216" t="n">
         <v>1400</v>
@@ -7358,7 +7358,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G241" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H241" t="n">
         <v>1400</v>
@@ -7387,7 +7387,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G243" t="n">
-        <v>4.30953645706177</v>
+        <v>4.30953598022461</v>
       </c>
       <c r="H243" t="n">
         <v>7350</v>
@@ -7967,7 +7967,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G262" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H262" t="n">
         <v>3500</v>
@@ -8228,7 +8228,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95693802833557</v>
+        <v>3.95693778991699</v>
       </c>
       <c r="H271" t="n">
         <v>700</v>
@@ -8373,7 +8373,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G276" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H276" t="n">
         <v>14000</v>
@@ -8402,7 +8402,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G277" t="n">
-        <v>3.60433959960938</v>
+        <v>3.6043393611908</v>
       </c>
       <c r="H277" t="n">
         <v>7000</v>
@@ -8489,7 +8489,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H280" t="n">
         <v>1050</v>
@@ -8518,7 +8518,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G281" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H281" t="n">
         <v>1750</v>
@@ -8547,7 +8547,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H282" t="n">
         <v>1050</v>
@@ -8779,7 +8779,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G290" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H290" t="n">
         <v>4900</v>
@@ -8808,7 +8808,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H291" t="n">
         <v>1050</v>
@@ -8837,7 +8837,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H292" t="n">
         <v>1750</v>
@@ -8866,7 +8866,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H293" t="n">
         <v>700</v>
@@ -8895,7 +8895,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G294" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H294" t="n">
         <v>700</v>
@@ -8953,7 +8953,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G296" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H296" t="n">
         <v>1400</v>
@@ -9040,7 +9040,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G299" t="n">
-        <v>3.70228362083435</v>
+        <v>3.70228338241577</v>
       </c>
       <c r="H299" t="n">
         <v>1400</v>
@@ -9156,7 +9156,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H303" t="n">
         <v>700</v>
@@ -9214,7 +9214,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H305" t="n">
         <v>2450</v>
@@ -9243,7 +9243,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G306" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H306" t="n">
         <v>5600</v>
@@ -9417,7 +9417,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>4.15282535552979</v>
+        <v>4.15282583236694</v>
       </c>
       <c r="H312" t="n">
         <v>4550</v>
@@ -9707,7 +9707,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G322" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H322" t="n">
         <v>1050</v>
@@ -9736,7 +9736,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G323" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G330" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H330" t="n">
         <v>2100</v>
@@ -9968,7 +9968,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H331" t="n">
         <v>4550</v>
@@ -9997,7 +9997,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G332" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H332" t="n">
         <v>2100</v>
@@ -10316,7 +10316,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H343" t="n">
         <v>3500</v>
@@ -10345,7 +10345,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G346" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H349" t="n">
         <v>350</v>
@@ -10519,7 +10519,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H351" t="n">
         <v>350</v>
@@ -10693,7 +10693,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G356" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H356" t="n">
         <v>4200</v>
@@ -10751,7 +10751,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G358" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H358" t="n">
         <v>7350</v>
@@ -10780,7 +10780,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G359" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H359" t="n">
         <v>8050</v>
@@ -11041,7 +11041,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>3.8981716632843</v>
+        <v>3.89817142486572</v>
       </c>
       <c r="H368" t="n">
         <v>1400</v>
@@ -11331,7 +11331,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>4.03529262542725</v>
+        <v>4.0352931022644</v>
       </c>
       <c r="H378" t="n">
         <v>1050</v>
@@ -11389,7 +11389,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G380" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H380" t="n">
         <v>2100</v>
@@ -11418,7 +11418,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G382" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G383" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H383" t="n">
         <v>350</v>
@@ -11505,7 +11505,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G384" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.78063869476318</v>
+        <v>3.7806384563446</v>
       </c>
       <c r="H385" t="n">
         <v>700</v>
@@ -11563,7 +11563,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G386" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H386" t="n">
         <v>11550</v>
@@ -11592,7 +11592,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G388" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>3.80022764205933</v>
+        <v>3.80022740364075</v>
       </c>
       <c r="H400" t="n">
         <v>2450</v>
@@ -11998,7 +11998,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H401" t="n">
         <v>350</v>
@@ -12027,7 +12027,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G403" t="n">
-        <v>3.81981635093689</v>
+        <v>3.81981658935547</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G408" t="n">
-        <v>3.70228362083435</v>
+        <v>3.70228338241577</v>
       </c>
       <c r="H408" t="n">
         <v>700</v>
@@ -12230,7 +12230,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G409" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H409" t="n">
         <v>1750</v>
@@ -12259,7 +12259,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G410" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12636,7 +12636,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G423" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H423" t="n">
         <v>350</v>
@@ -12665,7 +12665,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G424" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G425" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G426" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G427" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -12781,7 +12781,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G428" t="n">
-        <v>3.58475089073181</v>
+        <v>3.58475065231323</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G432" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H432" t="n">
         <v>2100</v>
@@ -12926,7 +12926,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G433" t="n">
-        <v>3.72187232971191</v>
+        <v>3.72187209129333</v>
       </c>
       <c r="H433" t="n">
         <v>7350</v>
@@ -12984,7 +12984,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G435" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H435" t="n">
         <v>6300</v>
@@ -13100,7 +13100,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G439" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H439" t="n">
         <v>700</v>
@@ -13129,7 +13129,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G440" t="n">
-        <v>4.17241477966309</v>
+        <v>4.17241525650024</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H442" t="n">
         <v>5950</v>
@@ -13216,7 +13216,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G443" t="n">
-        <v>4.21159219741821</v>
+        <v>4.21159267425537</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G444" t="n">
-        <v>4.32912492752075</v>
+        <v>4.32912540435791</v>
       </c>
       <c r="H444" t="n">
         <v>5600</v>
@@ -24126,6 +24126,64 @@
         <v>350</v>
       </c>
       <c r="I819" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="s">
+        <v>9</v>
+      </c>
+      <c r="B820" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C820" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="D820" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="E820" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="F820" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="G820" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="H820" t="n">
+        <v>0</v>
+      </c>
+      <c r="I820" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="s">
+        <v>9</v>
+      </c>
+      <c r="B821" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C821" t="n">
+        <v>9</v>
+      </c>
+      <c r="D821" t="n">
+        <v>9</v>
+      </c>
+      <c r="E821" t="n">
+        <v>8.94999980926514</v>
+      </c>
+      <c r="F821" t="n">
+        <v>9</v>
+      </c>
+      <c r="G821" t="n">
+        <v>9</v>
+      </c>
+      <c r="H821" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I821" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAG.MI.xlsx
+++ b/data/PAG.MI.xlsx
@@ -24187,6 +24187,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="822">
+      <c r="A822" t="s">
+        <v>9</v>
+      </c>
+      <c r="B822" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C822" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D822" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="E822" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F822" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="G822" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="H822" t="n">
+        <v>350</v>
+      </c>
+      <c r="I822" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
